--- a/Indomie Clients Details/Sohail Traders SD.xlsx
+++ b/Indomie Clients Details/Sohail Traders SD.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69BF7DEF-E368-45B8-A161-F14C538EAC82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA8629E5-0656-4420-B10A-9BED4B73143E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="949" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,6 +38,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'1'!$K$3:$P$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Cust. Price List'!$A$7:$Q$7</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'1'!$A$1:$Q$37</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
@@ -23836,7 +23837,7 @@
       </c>
       <c r="U14" s="163">
         <f>+'1'!P35</f>
-        <v>251898.372936</v>
+        <v>248050.38069600001</v>
       </c>
       <c r="XFD14" t="s">
         <v>75</v>
@@ -24366,23 +24367,23 @@
       </c>
       <c r="L22" s="174">
         <f>+'1'!L22+'2'!L22+'4'!L22+'3'!L22+'5'!L22+'6'!L22+'7'!L22+'8'!L22+'9'!L22+'10'!L22</f>
-        <v>3138.4000000000005</v>
+        <v>6276.8000000000011</v>
       </c>
       <c r="M22" s="117">
         <f t="shared" si="2"/>
-        <v>-5335.2800000000007</v>
+        <v>-8473.6800000000021</v>
       </c>
       <c r="N22" s="100">
         <f>+'1'!N22+'2'!N22+'4'!N22+'3'!N22+'5'!N22+'6'!N22+'7'!N22+'8'!N22+'9'!N22+'10'!N22</f>
-        <v>12635.198400000001</v>
+        <v>11944.750400000001</v>
       </c>
       <c r="O22" s="100">
         <f>+'1'!O22+'2'!O22+'4'!O22+'3'!O22+'5'!O22+'6'!O22+'7'!O22+'8'!O22+'9'!O22+'10'!O22</f>
-        <v>350.33959200000004</v>
+        <v>331.19535200000007</v>
       </c>
       <c r="P22" s="119">
         <f t="shared" si="0"/>
-        <v>7650.2579920000007</v>
+        <v>3802.2657519999989</v>
       </c>
       <c r="T22" s="162" t="str">
         <f>+'9'!A5</f>
@@ -24567,23 +24568,23 @@
       </c>
       <c r="L25" s="178">
         <f t="shared" si="3"/>
-        <v>31032.160000000003</v>
+        <v>34170.560000000005</v>
       </c>
       <c r="M25" s="140">
         <f t="shared" si="3"/>
-        <v>-33229.040000000001</v>
+        <v>-36367.440000000002</v>
       </c>
       <c r="N25" s="141">
         <f>SUM(N16:N24)</f>
-        <v>46770.1872</v>
+        <v>46079.739199999996</v>
       </c>
       <c r="O25" s="142">
         <f>SUM(O16:O24)</f>
-        <v>1253.2257360000001</v>
+        <v>1234.0814960000002</v>
       </c>
       <c r="P25" s="143">
         <f>SUM(P16:P24)</f>
-        <v>14794.372936</v>
+        <v>10946.380695999998</v>
       </c>
       <c r="T25" s="162" t="str">
         <f>+'12'!A5</f>
@@ -24791,7 +24792,7 @@
       </c>
       <c r="U33" s="164">
         <f>SUM(U14:U28)</f>
-        <v>251898.372936</v>
+        <v>248050.38069600001</v>
       </c>
     </row>
     <row r="34" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -24845,7 +24846,7 @@
       <c r="O36" s="241"/>
       <c r="P36" s="152">
         <f>L25</f>
-        <v>31032.160000000003</v>
+        <v>34170.560000000005</v>
       </c>
     </row>
     <row r="37" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24888,7 +24889,7 @@
       <c r="O38" s="241"/>
       <c r="P38" s="152">
         <f>P35-P36-P37</f>
-        <v>-33229.040000000001</v>
+        <v>-36367.440000000002</v>
       </c>
     </row>
     <row r="39" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24913,7 +24914,7 @@
       </c>
       <c r="P39" s="152">
         <f>N25</f>
-        <v>46770.1872</v>
+        <v>46079.739199999996</v>
       </c>
     </row>
     <row r="40" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24935,7 +24936,7 @@
       <c r="O40" s="243"/>
       <c r="P40" s="152">
         <f>P38+P39</f>
-        <v>13541.147199999999</v>
+        <v>9712.299199999994</v>
       </c>
     </row>
     <row r="41" spans="1:21" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -24960,7 +24961,7 @@
       </c>
       <c r="P41" s="152">
         <f>O41*P40</f>
-        <v>338.52868000000001</v>
+        <v>242.80747999999986</v>
       </c>
     </row>
     <row r="42" spans="1:21" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -24970,7 +24971,7 @@
       <c r="O42" s="221"/>
       <c r="P42" s="159">
         <f>P40+P41</f>
-        <v>13879.675879999999</v>
+        <v>9955.1066799999935</v>
       </c>
     </row>
     <row r="43" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -25834,24 +25835,24 @@
         <v>2196.8800000000006</v>
       </c>
       <c r="L22" s="119">
-        <f>I22*5%</f>
-        <v>3138.4000000000005</v>
+        <f>I22*10%</f>
+        <v>6276.8000000000011</v>
       </c>
       <c r="M22" s="117">
         <f t="shared" si="6"/>
-        <v>57432.720000000008</v>
+        <v>54294.320000000007</v>
       </c>
       <c r="N22" s="117">
         <f t="shared" si="0"/>
-        <v>12635.198400000001</v>
+        <v>11944.750400000001</v>
       </c>
       <c r="O22" s="118">
         <f t="shared" si="1"/>
-        <v>350.33959200000004</v>
+        <v>331.19535200000007</v>
       </c>
       <c r="P22" s="119">
         <f t="shared" si="2"/>
-        <v>70418.257992000013</v>
+        <v>66570.265752000007</v>
       </c>
     </row>
     <row r="23" spans="1:19 16384:16384" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -25997,23 +25998,23 @@
       </c>
       <c r="L25" s="139">
         <f t="shared" si="10"/>
-        <v>31032.160000000003</v>
+        <v>34170.560000000005</v>
       </c>
       <c r="M25" s="140">
         <f t="shared" si="10"/>
-        <v>203874.96</v>
+        <v>200736.56</v>
       </c>
       <c r="N25" s="141">
         <f>SUM(N16:N24)</f>
-        <v>46770.1872</v>
+        <v>46079.739199999996</v>
       </c>
       <c r="O25" s="142">
         <f>SUM(O16:O24)</f>
-        <v>1253.2257360000001</v>
+        <v>1234.0814960000002</v>
       </c>
       <c r="P25" s="143">
         <f>SUM(P16:P24)</f>
-        <v>251898.372936</v>
+        <v>248050.38069599998</v>
       </c>
     </row>
     <row r="26" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -26084,7 +26085,7 @@
       <c r="O29" s="241"/>
       <c r="P29" s="152">
         <f>L25</f>
-        <v>31032.160000000003</v>
+        <v>34170.560000000005</v>
       </c>
     </row>
     <row r="30" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -26127,7 +26128,7 @@
       <c r="O31" s="241"/>
       <c r="P31" s="152">
         <f>P28-P29-P30</f>
-        <v>203874.96</v>
+        <v>200736.56</v>
       </c>
     </row>
     <row r="32" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -26152,7 +26153,7 @@
       </c>
       <c r="P32" s="152">
         <f>N25</f>
-        <v>46770.1872</v>
+        <v>46079.739199999996</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -26174,7 +26175,7 @@
       <c r="O33" s="243"/>
       <c r="P33" s="152">
         <f>P31+P32</f>
-        <v>250645.14720000001</v>
+        <v>246816.29920000001</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -26199,7 +26200,7 @@
       </c>
       <c r="P34" s="152">
         <f>O34*P33</f>
-        <v>1253.2257360000001</v>
+        <v>1234.081496</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -26209,7 +26210,7 @@
       <c r="O35" s="221"/>
       <c r="P35" s="159">
         <f>P33+P34</f>
-        <v>251898.372936</v>
+        <v>248050.38069600001</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -26289,7 +26290,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="10" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <pageSetup scale="83" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
